--- a/examples/M485E_Test/M485E_Test_Reference.xlsx
+++ b/examples/M485E_Test/M485E_Test_Reference.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd737046c84b445a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DeviceMap" sheetId="2" r:id="R57e96fe7a18d4598"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModbusRule" sheetId="3" r:id="Rfe2086875e2a49b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EmulatorMap" sheetId="4" r:id="R1a97a31169bb4885"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SystemVariables" sheetId="5" r:id="R33f565bfc4e44fa7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb28ebebcb96e4819"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M485E_DeviceMap" sheetId="2" r:id="R8c1b7e468eaa4b95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M485E_FrameRule" sheetId="3" r:id="R3072acfbcf85400e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M485E_RegisterMap" sheetId="4" r:id="R4091b42c6636422c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SystemVariables" sheetId="5" r:id="Rb9041c267d5a46f1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -740,7 +740,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e2efe5cb2e042b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4db8b6d4ded14580"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1460,7 +1460,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55efe09401864516"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3246e13d2b64cc0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18786,7 +18786,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a571215e94640b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R074aeca984944036"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19775,7 +19775,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K30" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L30" s="32" t="str">
         <x:v>Chiller selected SignalName</x:v>
@@ -19811,7 +19811,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K31" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L31" s="32" t="str">
         <x:v>Chiller selected literal address</x:v>
@@ -19847,7 +19847,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K32" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L32" s="32" t="str">
         <x:v>Chiller selected physical value</x:v>
@@ -20027,7 +20027,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K37" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L37" s="32" t="str">
         <x:v>E-HVAC selected SignalName</x:v>
@@ -20063,7 +20063,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K38" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L38" s="32" t="str">
         <x:v>E-HVAC selected literal address</x:v>
@@ -20099,7 +20099,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K39" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L39" s="32" t="str">
         <x:v>E-HVAC selected physical value</x:v>
@@ -20279,7 +20279,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K44" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L44" s="32" t="str">
         <x:v>B-HVAC-1 selected SignalName</x:v>
@@ -20315,7 +20315,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K45" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L45" s="32" t="str">
         <x:v>B-HVAC-1 selected literal address</x:v>
@@ -20351,7 +20351,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K46" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L46" s="32" t="str">
         <x:v>B-HVAC-1 selected physical value</x:v>
@@ -20531,7 +20531,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="K51" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L51" s="32" t="str">
         <x:v>B-HVAC-2 selected SignalName</x:v>
@@ -20567,7 +20567,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="K52" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L52" s="32" t="str">
         <x:v>B-HVAC-2 selected literal address</x:v>
@@ -20603,7 +20603,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="K53" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L53" s="32" t="str">
         <x:v>B-HVAC-2 selected physical value</x:v>
@@ -20783,7 +20783,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K58" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L58" s="32" t="str">
         <x:v>B-HVAC-3 selected SignalName</x:v>
@@ -20819,7 +20819,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K59" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L59" s="32" t="str">
         <x:v>B-HVAC-3 selected literal address</x:v>
@@ -20855,7 +20855,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K60" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L60" s="32" t="str">
         <x:v>B-HVAC-3 selected physical value</x:v>
@@ -21035,7 +21035,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K65" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L65" s="32" t="str">
         <x:v>Gas Detector-1 selected SignalName</x:v>
@@ -21071,7 +21071,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K66" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L66" s="32" t="str">
         <x:v>Gas Detector-1 selected literal address</x:v>
@@ -21107,7 +21107,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K67" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L67" s="32" t="str">
         <x:v>Gas Detector-1 selected physical value</x:v>
@@ -21287,7 +21287,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="K72" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L72" s="32" t="str">
         <x:v>Gas Detector-2 selected SignalName</x:v>
@@ -21323,7 +21323,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="K73" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L73" s="32" t="str">
         <x:v>Gas Detector-2 selected literal address</x:v>
@@ -21359,7 +21359,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="K74" s="31" t="str">
-        <x:v>Modbus485EmulMap.csv</x:v>
+        <x:v>M485E_RegisterMap.csv</x:v>
       </x:c>
       <x:c r="L74" s="32" t="str">
         <x:v>Gas Detector-2 selected physical value</x:v>
@@ -21514,7 +21514,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ef862e51cc948dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6f858d1b5194bf6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/examples/M485E_Test/M485E_Test_Reference.xlsx
+++ b/examples/M485E_Test/M485E_Test_Reference.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra2e369d82c174a40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M485E_Device" sheetId="2" r:id="R42e4fd8af26c456a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M485E_FrameRule" sheetId="3" r:id="R726b7752b7864278"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RegisterMaps" sheetId="4" r:id="Re8750702e02047c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SystemVariables" sheetId="5" r:id="R628d6ad4b7d04fca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rae2037b48373412f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M485E_Device" sheetId="2" r:id="R6cece77c58a04a96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M485E_FrameRule" sheetId="3" r:id="R6a5e1b8c7f5346a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RegisterMaps" sheetId="4" r:id="R52c62d80bb344ddf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SystemVariables" sheetId="5" r:id="R0d7d5d80c91a4ede"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -33,7 +33,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -43,6 +43,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F75B5"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -85,7 +90,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -130,11 +135,39 @@
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SystemVariablesTable" displayName="SystemVariablesTable" ref="A1:H33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="8">
+    <x:tableColumn id="1" name="Namespace"/>
+    <x:tableColumn id="2" name="Name"/>
+    <x:tableColumn id="3" name="Full_Name"/>
+    <x:tableColumn id="4" name="Type"/>
+    <x:tableColumn id="5" name="Array_Length"/>
+    <x:tableColumn id="6" name="Default"/>
+    <x:tableColumn id="7" name="Panel_Control"/>
+    <x:tableColumn id="8" name="Description"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -339,7 +372,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Modbus485Emulator Test Configuration</x:v>
+        <x:v>Modbus485Emulator v0.3.0 Test Configuration</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -409,7 +442,7 @@
         <x:v>M485E_SystemVariables.csv</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
         <x:v>Shared</x:v>
@@ -918,643 +951,816 @@
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="46" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="54" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="46" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="16" t="str">
+      <x:c r="A1" s="20" t="str">
         <x:v>Namespace</x:v>
       </x:c>
-      <x:c r="B1" s="16" t="str">
+      <x:c r="B1" s="20" t="str">
         <x:v>Name</x:v>
       </x:c>
-      <x:c r="C1" s="16" t="str">
+      <x:c r="C1" s="20" t="str">
         <x:v>Full_Name</x:v>
       </x:c>
-      <x:c r="D1" s="16" t="str">
+      <x:c r="D1" s="20" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="E1" s="16" t="str">
+      <x:c r="E1" s="20" t="str">
         <x:v>Array_Length</x:v>
       </x:c>
-      <x:c r="F1" s="16" t="str">
+      <x:c r="F1" s="20" t="str">
         <x:v>Default</x:v>
       </x:c>
-      <x:c r="G1" s="16" t="str">
+      <x:c r="G1" s="20" t="str">
         <x:v>Panel_Control</x:v>
       </x:c>
-      <x:c r="H1" s="16" t="str">
+      <x:c r="H1" s="20" t="str">
         <x:v>Description</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="17" t="str">
+      <x:c r="A2" s="22" t="str">
         <x:v>M485E::Connection</x:v>
       </x:c>
-      <x:c r="B2" s="17" t="str">
+      <x:c r="B2" s="22" t="str">
         <x:v>ConnectSwitch</x:v>
       </x:c>
-      <x:c r="C2" s="17" t="str">
+      <x:c r="C2" s="22" t="str">
         <x:v>M485E::Connection::ConnectSwitch</x:v>
       </x:c>
-      <x:c r="D2" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E2" s="17" t="str"/>
-      <x:c r="F2" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="17" t="str">
+      <x:c r="D2" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E2" s="22" t="str"/>
+      <x:c r="F2" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2" s="22" t="str">
         <x:v>Toggle</x:v>
       </x:c>
-      <x:c r="H2" s="19" t="str">
+      <x:c r="H2" s="22" t="str">
         <x:v>Connection request</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="17" t="str">
+      <x:c r="A3" s="22" t="str">
         <x:v>M485E::Connection</x:v>
       </x:c>
-      <x:c r="B3" s="17" t="str">
+      <x:c r="B3" s="22" t="str">
         <x:v>Refresh</x:v>
       </x:c>
-      <x:c r="C3" s="17" t="str">
+      <x:c r="C3" s="22" t="str">
         <x:v>M485E::Connection::Refresh</x:v>
       </x:c>
-      <x:c r="D3" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E3" s="17" t="str"/>
-      <x:c r="F3" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="17" t="str">
+      <x:c r="D3" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E3" s="22" t="str"/>
+      <x:c r="F3" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G3" s="22" t="str">
         <x:v>Momentary button</x:v>
       </x:c>
-      <x:c r="H3" s="19" t="str">
+      <x:c r="H3" s="22" t="str">
         <x:v>CSV refresh request while disconnected</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
-      <x:c r="A4" s="17" t="str">
+      <x:c r="A4" s="22" t="str">
         <x:v>M485E::Connection</x:v>
       </x:c>
-      <x:c r="B4" s="17" t="str">
+      <x:c r="B4" s="22" t="str">
         <x:v>State</x:v>
       </x:c>
-      <x:c r="C4" s="17" t="str">
+      <x:c r="C4" s="22" t="str">
         <x:v>M485E::Connection::State</x:v>
       </x:c>
-      <x:c r="D4" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E4" s="17" t="str"/>
-      <x:c r="F4" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="17" t="str">
+      <x:c r="D4" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E4" s="22" t="str"/>
+      <x:c r="F4" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G4" s="22" t="str">
         <x:v>Numeric display</x:v>
       </x:c>
-      <x:c r="H4" s="19" t="str">
+      <x:c r="H4" s="22" t="str">
         <x:v>DLL lifecycle state</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="17" t="str">
+      <x:c r="A5" s="22" t="str">
         <x:v>M485E::Connection</x:v>
       </x:c>
-      <x:c r="B5" s="17" t="str">
+      <x:c r="B5" s="22" t="str">
         <x:v>LastResult</x:v>
       </x:c>
-      <x:c r="C5" s="17" t="str">
+      <x:c r="C5" s="22" t="str">
         <x:v>M485E::Connection::LastResult</x:v>
       </x:c>
-      <x:c r="D5" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E5" s="17" t="str"/>
-      <x:c r="F5" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="17" t="str">
+      <x:c r="D5" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E5" s="22" t="str"/>
+      <x:c r="F5" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5" s="22" t="str">
         <x:v>Numeric display</x:v>
       </x:c>
-      <x:c r="H5" s="19" t="str">
+      <x:c r="H5" s="22" t="str">
         <x:v>Last completed lifecycle result</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="17" t="str">
+      <x:c r="A6" s="22" t="str">
         <x:v>M485E::Connection</x:v>
       </x:c>
-      <x:c r="B6" s="17" t="str">
+      <x:c r="B6" s="22" t="str">
         <x:v>ConfigurationValid</x:v>
       </x:c>
-      <x:c r="C6" s="17" t="str">
+      <x:c r="C6" s="22" t="str">
         <x:v>M485E::Connection::ConfigurationValid</x:v>
       </x:c>
-      <x:c r="D6" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E6" s="17" t="str"/>
-      <x:c r="F6" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="17" t="str">
+      <x:c r="D6" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E6" s="22" t="str"/>
+      <x:c r="F6" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="22" t="str">
         <x:v>LED</x:v>
       </x:c>
-      <x:c r="H6" s="19" t="str">
+      <x:c r="H6" s="22" t="str">
         <x:v>CSV validation status</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="17" t="str">
+      <x:c r="A7" s="22" t="str">
         <x:v>M485E::Connection</x:v>
       </x:c>
-      <x:c r="B7" s="17" t="str">
+      <x:c r="B7" s="22" t="str">
         <x:v>ResultCode</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="str">
+      <x:c r="C7" s="22" t="str">
         <x:v>M485E::Connection::ResultCode</x:v>
       </x:c>
-      <x:c r="D7" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E7" s="17" t="str"/>
-      <x:c r="F7" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="str">
+      <x:c r="D7" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E7" s="22" t="str"/>
+      <x:c r="F7" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7" s="22" t="str">
         <x:v>Numeric display</x:v>
       </x:c>
-      <x:c r="H7" s="19" t="str">
+      <x:c r="H7" s="22" t="str">
         <x:v>Last command acceptance result</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="17" t="str">
+      <x:c r="A8" s="22" t="str">
         <x:v>M485E::Connection</x:v>
       </x:c>
-      <x:c r="B8" s="17" t="str">
+      <x:c r="B8" s="22" t="str">
         <x:v>ConnectedLed</x:v>
       </x:c>
-      <x:c r="C8" s="17" t="str">
+      <x:c r="C8" s="22" t="str">
         <x:v>M485E::Connection::ConnectedLed</x:v>
       </x:c>
-      <x:c r="D8" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E8" s="17" t="str"/>
-      <x:c r="F8" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="17" t="str">
+      <x:c r="D8" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E8" s="22" t="str"/>
+      <x:c r="F8" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="22" t="str">
         <x:v>Green LED</x:v>
       </x:c>
-      <x:c r="H8" s="19" t="str">
+      <x:c r="H8" s="22" t="str">
         <x:v>Actual connected state</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="17" t="str">
+      <x:c r="A9" s="22" t="str">
         <x:v>M485E::Connection</x:v>
       </x:c>
-      <x:c r="B9" s="17" t="str">
-        <x:v>BusyLed</x:v>
-      </x:c>
-      <x:c r="C9" s="17" t="str">
-        <x:v>M485E::Connection::BusyLed</x:v>
-      </x:c>
-      <x:c r="D9" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E9" s="17" t="str"/>
-      <x:c r="F9" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="17" t="str">
-        <x:v>Amber LED</x:v>
-      </x:c>
-      <x:c r="H9" s="19" t="str">
-        <x:v>Lifecycle operation in progress</x:v>
+      <x:c r="B9" s="22" t="str">
+        <x:v>DisconnectedLed</x:v>
+      </x:c>
+      <x:c r="C9" s="22" t="str">
+        <x:v>M485E::Connection::DisconnectedLed</x:v>
+      </x:c>
+      <x:c r="D9" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E9" s="22" t="str"/>
+      <x:c r="F9" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="22" t="str">
+        <x:v>Gray LED</x:v>
+      </x:c>
+      <x:c r="H9" s="22" t="str">
+        <x:v>Actual disconnected state</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="17" t="str">
+      <x:c r="A10" s="22" t="str">
         <x:v>M485E::Connection</x:v>
       </x:c>
-      <x:c r="B10" s="17" t="str">
-        <x:v>ErrorLed</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="str">
-        <x:v>M485E::Connection::ErrorLed</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E10" s="17" t="str"/>
-      <x:c r="F10" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="str">
-        <x:v>Red LED</x:v>
-      </x:c>
-      <x:c r="H10" s="19" t="str">
-        <x:v>Lifecycle error state</x:v>
+      <x:c r="B10" s="22" t="str">
+        <x:v>StateText</x:v>
+      </x:c>
+      <x:c r="C10" s="22" t="str">
+        <x:v>M485E::Connection::StateText</x:v>
+      </x:c>
+      <x:c r="D10" s="22" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="E10" s="22" t="str"/>
+      <x:c r="F10" s="22" t="str">
+        <x:v>Uninitialized</x:v>
+      </x:c>
+      <x:c r="G10" s="22" t="str">
+        <x:v>Text display</x:v>
+      </x:c>
+      <x:c r="H10" s="22" t="str">
+        <x:v>Readable lifecycle state</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="17" t="str">
-        <x:v>M485E::Connection</x:v>
-      </x:c>
-      <x:c r="B11" s="17" t="str">
-        <x:v>StateText</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="str">
-        <x:v>M485E::Connection::StateText</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="str">
+      <x:c r="A11" s="22" t="str">
+        <x:v>M485E::DeviceCommunication</x:v>
+      </x:c>
+      <x:c r="B11" s="22" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="str">
+        <x:v>M485E::DeviceCommunication::Enabled</x:v>
+      </x:c>
+      <x:c r="D11" s="22" t="str">
+        <x:v>int32[]</x:v>
+      </x:c>
+      <x:c r="E11" s="22" t="str">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F11" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="22" t="str">
+        <x:v>Device toggles</x:v>
+      </x:c>
+      <x:c r="H11" s="22" t="str">
+        <x:v>Per-Index external RTU communication enable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="22" t="str">
+        <x:v>M485E::DeviceCommunication</x:v>
+      </x:c>
+      <x:c r="B12" s="22" t="str">
+        <x:v>AvailableLed</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="str">
+        <x:v>M485E::DeviceCommunication::AvailableLed</x:v>
+      </x:c>
+      <x:c r="D12" s="22" t="str">
+        <x:v>int32[]</x:v>
+      </x:c>
+      <x:c r="E12" s="22" t="str">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F12" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="22" t="str">
+        <x:v>Green LED array</x:v>
+      </x:c>
+      <x:c r="H12" s="22" t="str">
+        <x:v>Per-Index RTU availability</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="22" t="str">
+        <x:v>M485E::DeviceCommunication</x:v>
+      </x:c>
+      <x:c r="B13" s="22" t="str">
+        <x:v>ResultCode</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="str">
+        <x:v>M485E::DeviceCommunication::ResultCode</x:v>
+      </x:c>
+      <x:c r="D13" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E13" s="22" t="str"/>
+      <x:c r="F13" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="22" t="str">
+        <x:v>Numeric display</x:v>
+      </x:c>
+      <x:c r="H13" s="22" t="str">
+        <x:v>Last device communication command result</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="22" t="str">
+        <x:v>M485E::RtuLog</x:v>
+      </x:c>
+      <x:c r="B14" s="22" t="str">
+        <x:v>LogSwitch</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="str">
+        <x:v>M485E::RtuLog::LogSwitch</x:v>
+      </x:c>
+      <x:c r="D14" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E14" s="22" t="str"/>
+      <x:c r="F14" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G14" s="22" t="str">
+        <x:v>Toggle</x:v>
+      </x:c>
+      <x:c r="H14" s="22" t="str">
+        <x:v>RTU CSV capture request</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="22" t="str">
+        <x:v>M485E::RtuLog</x:v>
+      </x:c>
+      <x:c r="B15" s="22" t="str">
+        <x:v>ActiveLed</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="str">
+        <x:v>M485E::RtuLog::ActiveLed</x:v>
+      </x:c>
+      <x:c r="D15" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E15" s="22" t="str"/>
+      <x:c r="F15" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="22" t="str">
+        <x:v>Green LED</x:v>
+      </x:c>
+      <x:c r="H15" s="22" t="str">
+        <x:v>Log file capture or drain active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="22" t="str">
+        <x:v>M485E::RtuLog</x:v>
+      </x:c>
+      <x:c r="B16" s="22" t="str">
+        <x:v>ResultCode</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="str">
+        <x:v>M485E::RtuLog::ResultCode</x:v>
+      </x:c>
+      <x:c r="D16" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E16" s="22" t="str"/>
+      <x:c r="F16" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="22" t="str">
+        <x:v>Numeric display</x:v>
+      </x:c>
+      <x:c r="H16" s="22" t="str">
+        <x:v>Last RTU log result</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="22" t="str">
+        <x:v>M485E::RtuLog</x:v>
+      </x:c>
+      <x:c r="B17" s="22" t="str">
+        <x:v>DroppedCount</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="str">
+        <x:v>M485E::RtuLog::DroppedCount</x:v>
+      </x:c>
+      <x:c r="D17" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E17" s="22" t="str"/>
+      <x:c r="F17" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="22" t="str">
+        <x:v>Numeric display</x:v>
+      </x:c>
+      <x:c r="H17" s="22" t="str">
+        <x:v>Dropped RTU transaction count</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="22" t="str">
+        <x:v>M485E::RtuLog</x:v>
+      </x:c>
+      <x:c r="B18" s="22" t="str">
+        <x:v>CurrentFileName</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="str">
+        <x:v>M485E::RtuLog::CurrentFileName</x:v>
+      </x:c>
+      <x:c r="D18" s="22" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="E11" s="17" t="str"/>
-      <x:c r="F11" s="17" t="str">
-        <x:v>Uninitialized</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="str">
+      <x:c r="E18" s="22" t="str"/>
+      <x:c r="F18" s="22" t="str"/>
+      <x:c r="G18" s="22" t="str">
         <x:v>Text display</x:v>
       </x:c>
-      <x:c r="H11" s="19" t="str">
-        <x:v>Readable lifecycle state</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="17" t="str">
+      <x:c r="H18" s="22" t="str">
+        <x:v>Last RTU CSV file name</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="22" t="str">
         <x:v>M485E::Monitoring</x:v>
       </x:c>
-      <x:c r="B12" s="17" t="str">
+      <x:c r="B19" s="22" t="str">
         <x:v>ReadSwitch</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="str">
+      <x:c r="C19" s="22" t="str">
         <x:v>M485E::Monitoring::ReadSwitch</x:v>
       </x:c>
-      <x:c r="D12" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="str"/>
-      <x:c r="F12" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="str">
+      <x:c r="D19" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E19" s="22" t="str"/>
+      <x:c r="F19" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="22" t="str">
         <x:v>Toggle</x:v>
       </x:c>
-      <x:c r="H12" s="19" t="str">
+      <x:c r="H19" s="22" t="str">
         <x:v>Monitoring master switch</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="17" t="str">
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="22" t="str">
         <x:v>M485E::Monitoring</x:v>
       </x:c>
-      <x:c r="B13" s="17" t="str">
+      <x:c r="B20" s="22" t="str">
         <x:v>Check_ReadOption</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="str">
+      <x:c r="C20" s="22" t="str">
         <x:v>M485E::Monitoring::Check_ReadOption</x:v>
       </x:c>
-      <x:c r="D13" s="17" t="str">
+      <x:c r="D20" s="22" t="str">
         <x:v>int32[]</x:v>
       </x:c>
-      <x:c r="E13" s="17" t="str">
+      <x:c r="E20" s="22" t="str">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="F13" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="str">
+      <x:c r="F20" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G20" s="22" t="str">
         <x:v>Rule checkboxes</x:v>
       </x:c>
-      <x:c r="H13" s="19" t="str">
+      <x:c r="H20" s="22" t="str">
         <x:v>Periodic Rule selection</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="17" t="str">
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="22" t="str">
         <x:v>M485E::Monitoring</x:v>
       </x:c>
-      <x:c r="B14" s="17" t="str">
+      <x:c r="B21" s="22" t="str">
         <x:v>ResultCode</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="str">
+      <x:c r="C21" s="22" t="str">
         <x:v>M485E::Monitoring::ResultCode</x:v>
       </x:c>
-      <x:c r="D14" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="str"/>
-      <x:c r="F14" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="str">
+      <x:c r="D21" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E21" s="22" t="str"/>
+      <x:c r="F21" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G21" s="22" t="str">
         <x:v>Numeric display</x:v>
       </x:c>
-      <x:c r="H14" s="19" t="str">
+      <x:c r="H21" s="22" t="str">
         <x:v>Last monitoring result</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="15" hidden="0" customHeight="1">
-      <x:c r="A15" s="17" t="str">
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" s="22" t="str">
         <x:v>M485E::ManualWrite</x:v>
       </x:c>
-      <x:c r="B15" s="17" t="str">
+      <x:c r="B22" s="22" t="str">
         <x:v>Index</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="str">
+      <x:c r="C22" s="22" t="str">
         <x:v>M485E::ManualWrite::Index</x:v>
       </x:c>
-      <x:c r="D15" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E15" s="17" t="str"/>
-      <x:c r="F15" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="str">
+      <x:c r="D22" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E22" s="22" t="str"/>
+      <x:c r="F22" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G22" s="22" t="str">
         <x:v>Numeric input</x:v>
       </x:c>
-      <x:c r="H15" s="19" t="str">
+      <x:c r="H22" s="22" t="str">
         <x:v>Device Index</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="17" t="str">
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
+      <x:c r="A23" s="22" t="str">
         <x:v>M485E::ManualWrite</x:v>
       </x:c>
-      <x:c r="B16" s="17" t="str">
+      <x:c r="B23" s="22" t="str">
         <x:v>StartAddress</x:v>
       </x:c>
-      <x:c r="C16" s="17" t="str">
+      <x:c r="C23" s="22" t="str">
         <x:v>M485E::ManualWrite::StartAddress</x:v>
       </x:c>
-      <x:c r="D16" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E16" s="17" t="str"/>
-      <x:c r="F16" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="17" t="str">
+      <x:c r="D23" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E23" s="22" t="str"/>
+      <x:c r="F23" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G23" s="22" t="str">
         <x:v>Numeric input</x:v>
       </x:c>
-      <x:c r="H16" s="19" t="str">
+      <x:c r="H23" s="22" t="str">
         <x:v>Literal start address</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="17" t="str">
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
+      <x:c r="A24" s="22" t="str">
         <x:v>M485E::ManualWrite</x:v>
       </x:c>
-      <x:c r="B17" s="17" t="str">
+      <x:c r="B24" s="22" t="str">
         <x:v>Quantity</x:v>
       </x:c>
-      <x:c r="C17" s="17" t="str">
+      <x:c r="C24" s="22" t="str">
         <x:v>M485E::ManualWrite::Quantity</x:v>
       </x:c>
-      <x:c r="D17" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E17" s="17" t="str"/>
-      <x:c r="F17" s="17" t="str">
+      <x:c r="D24" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E24" s="22" t="str"/>
+      <x:c r="F24" s="22" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G17" s="17" t="str">
+      <x:c r="G24" s="22" t="str">
         <x:v>Numeric input</x:v>
       </x:c>
-      <x:c r="H17" s="19" t="str">
+      <x:c r="H24" s="22" t="str">
         <x:v>Register count from 1 to 122</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="17" t="str">
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" s="22" t="str">
         <x:v>M485E::ManualWrite</x:v>
       </x:c>
-      <x:c r="B18" s="17" t="str">
+      <x:c r="B25" s="22" t="str">
         <x:v>Data</x:v>
       </x:c>
-      <x:c r="C18" s="17" t="str">
+      <x:c r="C25" s="22" t="str">
         <x:v>M485E::ManualWrite::Data</x:v>
       </x:c>
-      <x:c r="D18" s="17" t="str">
+      <x:c r="D25" s="22" t="str">
         <x:v>int32[]</x:v>
       </x:c>
-      <x:c r="E18" s="17" t="str">
+      <x:c r="E25" s="22" t="str">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="F18" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="str">
+      <x:c r="F25" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G25" s="22" t="str">
         <x:v>Array input</x:v>
       </x:c>
-      <x:c r="H18" s="19" t="str">
+      <x:c r="H25" s="22" t="str">
         <x:v>Register values stored in 32-bit elements</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="17" t="str">
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
+      <x:c r="A26" s="22" t="str">
         <x:v>M485E::ManualWrite</x:v>
       </x:c>
-      <x:c r="B19" s="17" t="str">
+      <x:c r="B26" s="22" t="str">
         <x:v>Send</x:v>
       </x:c>
-      <x:c r="C19" s="17" t="str">
+      <x:c r="C26" s="22" t="str">
         <x:v>M485E::ManualWrite::Send</x:v>
       </x:c>
-      <x:c r="D19" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E19" s="17" t="str"/>
-      <x:c r="F19" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="str">
+      <x:c r="D26" s="22" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E26" s="22" t="str"/>
+      <x:c r="F26" s="22" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G26" s="22" t="str">
         <x:v>Momentary button</x:v>
       </x:c>
-      <x:c r="H19" s="19" t="str">
+      <x:c r="H26" s="22" t="str">
         <x:v>Manual Register Write command</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="15" hidden="0" customHeight="1">
-      <x:c r="A20" s="17" t="str">
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="23" t="str">
         <x:v>M485E::ManualWrite</x:v>
       </x:c>
-      <x:c r="B20" s="17" t="str">
+      <x:c r="B27" s="23" t="str">
         <x:v>ResultCode</x:v>
       </x:c>
-      <x:c r="C20" s="17" t="str">
+      <x:c r="C27" s="23" t="str">
         <x:v>M485E::ManualWrite::ResultCode</x:v>
       </x:c>
-      <x:c r="D20" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E20" s="17" t="str"/>
-      <x:c r="F20" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="17" t="str">
+      <x:c r="D27" s="23" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E27" s="23" t="str"/>
+      <x:c r="F27" s="23" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G27" s="23" t="str">
         <x:v>Numeric display</x:v>
       </x:c>
-      <x:c r="H20" s="19" t="str">
+      <x:c r="H27" s="23" t="str">
         <x:v>Manual Write result</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="15" hidden="0" customHeight="1">
-      <x:c r="A21" s="17" t="str">
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="23" t="str">
         <x:v>M485E::SignalControl</x:v>
       </x:c>
-      <x:c r="B21" s="17" t="str">
+      <x:c r="B28" s="23" t="str">
         <x:v>Index</x:v>
       </x:c>
-      <x:c r="C21" s="17" t="str">
+      <x:c r="C28" s="23" t="str">
         <x:v>M485E::SignalControl::Index</x:v>
       </x:c>
-      <x:c r="D21" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E21" s="17" t="str"/>
-      <x:c r="F21" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="17" t="str">
+      <x:c r="D28" s="23" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E28" s="23" t="str"/>
+      <x:c r="F28" s="23" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G28" s="23" t="str">
         <x:v>Numeric input</x:v>
       </x:c>
-      <x:c r="H21" s="19" t="str">
+      <x:c r="H28" s="23" t="str">
         <x:v>Device Index</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="15" hidden="0" customHeight="1">
-      <x:c r="A22" s="17" t="str">
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="23" t="str">
         <x:v>M485E::SignalControl</x:v>
       </x:c>
-      <x:c r="B22" s="17" t="str">
+      <x:c r="B29" s="23" t="str">
         <x:v>SignalName</x:v>
       </x:c>
-      <x:c r="C22" s="17" t="str">
+      <x:c r="C29" s="23" t="str">
         <x:v>M485E::SignalControl::SignalName</x:v>
       </x:c>
-      <x:c r="D22" s="17" t="str">
+      <x:c r="D29" s="23" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="E22" s="17" t="str"/>
-      <x:c r="F22" s="17" t="str"/>
-      <x:c r="G22" s="17" t="str">
+      <x:c r="E29" s="23" t="str"/>
+      <x:c r="F29" s="23" t="str"/>
+      <x:c r="G29" s="23" t="str">
         <x:v>Text input</x:v>
       </x:c>
-      <x:c r="H22" s="19" t="str">
+      <x:c r="H29" s="23" t="str">
         <x:v>Case-sensitive SignalName</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="15" hidden="0" customHeight="1">
-      <x:c r="A23" s="17" t="str">
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="23" t="str">
         <x:v>M485E::SignalControl</x:v>
       </x:c>
-      <x:c r="B23" s="17" t="str">
+      <x:c r="B30" s="23" t="str">
         <x:v>PhysicalValue</x:v>
       </x:c>
-      <x:c r="C23" s="17" t="str">
+      <x:c r="C30" s="23" t="str">
         <x:v>M485E::SignalControl::PhysicalValue</x:v>
       </x:c>
-      <x:c r="D23" s="17" t="str">
+      <x:c r="D30" s="23" t="str">
         <x:v>float64</x:v>
       </x:c>
-      <x:c r="E23" s="17" t="str"/>
-      <x:c r="F23" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="17" t="str">
+      <x:c r="E30" s="23" t="str"/>
+      <x:c r="F30" s="23" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G30" s="23" t="str">
         <x:v>Numeric input/display</x:v>
       </x:c>
-      <x:c r="H23" s="19" t="str">
+      <x:c r="H30" s="23" t="str">
         <x:v>Signal physical value</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="15" hidden="0" customHeight="1">
-      <x:c r="A24" s="17" t="str">
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
+      <x:c r="A31" s="23" t="str">
         <x:v>M485E::SignalControl</x:v>
       </x:c>
-      <x:c r="B24" s="17" t="str">
+      <x:c r="B31" s="23" t="str">
         <x:v>Read</x:v>
       </x:c>
-      <x:c r="C24" s="17" t="str">
+      <x:c r="C31" s="23" t="str">
         <x:v>M485E::SignalControl::Read</x:v>
       </x:c>
-      <x:c r="D24" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E24" s="17" t="str"/>
-      <x:c r="F24" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="17" t="str">
+      <x:c r="D31" s="23" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E31" s="23" t="str"/>
+      <x:c r="F31" s="23" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G31" s="23" t="str">
         <x:v>Momentary button</x:v>
       </x:c>
-      <x:c r="H24" s="19" t="str">
+      <x:c r="H31" s="23" t="str">
         <x:v>Signal Read command</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="15" hidden="0" customHeight="1">
-      <x:c r="A25" s="17" t="str">
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
+      <x:c r="A32" s="23" t="str">
         <x:v>M485E::SignalControl</x:v>
       </x:c>
-      <x:c r="B25" s="17" t="str">
+      <x:c r="B32" s="23" t="str">
         <x:v>Write</x:v>
       </x:c>
-      <x:c r="C25" s="17" t="str">
+      <x:c r="C32" s="23" t="str">
         <x:v>M485E::SignalControl::Write</x:v>
       </x:c>
-      <x:c r="D25" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E25" s="17" t="str"/>
-      <x:c r="F25" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="17" t="str">
+      <x:c r="D32" s="23" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E32" s="23" t="str"/>
+      <x:c r="F32" s="23" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G32" s="23" t="str">
         <x:v>Momentary button</x:v>
       </x:c>
-      <x:c r="H25" s="19" t="str">
+      <x:c r="H32" s="23" t="str">
         <x:v>Signal Write command</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="15" hidden="0" customHeight="1">
-      <x:c r="A26" s="17" t="str">
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
+      <x:c r="A33" s="23" t="str">
         <x:v>M485E::SignalControl</x:v>
       </x:c>
-      <x:c r="B26" s="17" t="str">
+      <x:c r="B33" s="23" t="str">
         <x:v>ResultCode</x:v>
       </x:c>
-      <x:c r="C26" s="17" t="str">
+      <x:c r="C33" s="23" t="str">
         <x:v>M485E::SignalControl::ResultCode</x:v>
       </x:c>
-      <x:c r="D26" s="17" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E26" s="17" t="str"/>
-      <x:c r="F26" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="17" t="str">
+      <x:c r="D33" s="23" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E33" s="23" t="str"/>
+      <x:c r="F33" s="23" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G33" s="23" t="str">
         <x:v>Numeric display</x:v>
       </x:c>
-      <x:c r="H26" s="19" t="str">
+      <x:c r="H33" s="23" t="str">
         <x:v>Signal operation result</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcad102da3a76426c"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
--- a/examples/M485E_Test/M485E_Test_Reference.xlsx
+++ b/examples/M485E_Test/M485E_Test_Reference.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rae2037b48373412f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M485E_Device" sheetId="2" r:id="R6cece77c58a04a96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M485E_FrameRule" sheetId="3" r:id="R6a5e1b8c7f5346a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RegisterMaps" sheetId="4" r:id="R52c62d80bb344ddf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SystemVariables" sheetId="5" r:id="R0d7d5d80c91a4ede"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4b2979a145d54da9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M485E_Device" sheetId="2" r:id="Ree66acddc92c4d86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M485E_FrameRule" sheetId="3" r:id="R54632d06515740e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RegisterMaps" sheetId="4" r:id="Rbbce05880bed42b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SystemVariables" sheetId="5" r:id="Rff1aa76042a84a24"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -372,7 +372,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Modbus485Emulator v0.3.0 Test Configuration</x:v>
+        <x:v>Modbus485Emulator v0.4.0 Test Configuration</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -1760,7 +1760,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcad102da3a76426c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c3d6ad5cd264dc2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/examples/M485E_Test/M485E_Test_Reference.xlsx
+++ b/examples/M485E_Test/M485E_Test_Reference.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4b2979a145d54da9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M485E_Device" sheetId="2" r:id="Ree66acddc92c4d86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M485E_FrameRule" sheetId="3" r:id="R54632d06515740e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RegisterMaps" sheetId="4" r:id="Rbbce05880bed42b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SystemVariables" sheetId="5" r:id="Rff1aa76042a84a24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Re696ea8b85fe4d2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M485E_Device" sheetId="2" r:id="R6b0988801167471a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M485E_FrameRule" sheetId="3" r:id="R70eec0fb1c674adb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RegisterMaps" sheetId="4" r:id="R82991a4102c2460b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SystemVariables" sheetId="5" r:id="R4ecd2407af1548ab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -372,7 +372,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Modbus485Emulator v0.4.0 Test Configuration</x:v>
+        <x:v>Modbus485Emulator v0.5.0 Test Configuration</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -442,7 +442,7 @@
         <x:v>M485E_SystemVariables.csv</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
         <x:v>Shared</x:v>
@@ -1424,25 +1424,23 @@
         <x:v>M485E::Monitoring</x:v>
       </x:c>
       <x:c r="B20" s="22" t="str">
-        <x:v>Check_ReadOption</x:v>
+        <x:v>Btn_ReadOption</x:v>
       </x:c>
       <x:c r="C20" s="22" t="str">
-        <x:v>M485E::Monitoring::Check_ReadOption</x:v>
+        <x:v>M485E::Monitoring::Btn_ReadOption</x:v>
       </x:c>
       <x:c r="D20" s="22" t="str">
-        <x:v>int32[]</x:v>
-      </x:c>
-      <x:c r="E20" s="22" t="str">
-        <x:v>200</x:v>
-      </x:c>
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E20" s="22" t="str"/>
       <x:c r="F20" s="22" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G20" s="22" t="str">
-        <x:v>Rule checkboxes</x:v>
+        <x:v>Momentary button</x:v>
       </x:c>
       <x:c r="H20" s="22" t="str">
-        <x:v>Periodic Rule selection</x:v>
+        <x:v>ReadOption checkbox convenience button without CAPL handler</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -1450,34 +1448,36 @@
         <x:v>M485E::Monitoring</x:v>
       </x:c>
       <x:c r="B21" s="22" t="str">
-        <x:v>ResultCode</x:v>
+        <x:v>Check_ReadOption</x:v>
       </x:c>
       <x:c r="C21" s="22" t="str">
-        <x:v>M485E::Monitoring::ResultCode</x:v>
+        <x:v>M485E::Monitoring::Check_ReadOption</x:v>
       </x:c>
       <x:c r="D21" s="22" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E21" s="22" t="str"/>
+        <x:v>int32[]</x:v>
+      </x:c>
+      <x:c r="E21" s="22" t="str">
+        <x:v>200</x:v>
+      </x:c>
       <x:c r="F21" s="22" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G21" s="22" t="str">
-        <x:v>Numeric display</x:v>
+        <x:v>Rule checkboxes</x:v>
       </x:c>
       <x:c r="H21" s="22" t="str">
-        <x:v>Last monitoring result</x:v>
+        <x:v>Periodic Rule selection</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="22" t="str">
-        <x:v>M485E::ManualWrite</x:v>
+        <x:v>M485E::Monitoring</x:v>
       </x:c>
       <x:c r="B22" s="22" t="str">
-        <x:v>Index</x:v>
+        <x:v>ResultCode</x:v>
       </x:c>
       <x:c r="C22" s="22" t="str">
-        <x:v>M485E::ManualWrite::Index</x:v>
+        <x:v>M485E::Monitoring::ResultCode</x:v>
       </x:c>
       <x:c r="D22" s="22" t="str">
         <x:v>int32</x:v>
@@ -1487,10 +1487,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G22" s="22" t="str">
-        <x:v>Numeric input</x:v>
+        <x:v>Numeric display</x:v>
       </x:c>
       <x:c r="H22" s="22" t="str">
-        <x:v>Device Index</x:v>
+        <x:v>Last monitoring result</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -1498,10 +1498,10 @@
         <x:v>M485E::ManualWrite</x:v>
       </x:c>
       <x:c r="B23" s="22" t="str">
-        <x:v>StartAddress</x:v>
+        <x:v>Index</x:v>
       </x:c>
       <x:c r="C23" s="22" t="str">
-        <x:v>M485E::ManualWrite::StartAddress</x:v>
+        <x:v>M485E::ManualWrite::Index</x:v>
       </x:c>
       <x:c r="D23" s="22" t="str">
         <x:v>int32</x:v>
@@ -1514,7 +1514,7 @@
         <x:v>Numeric input</x:v>
       </x:c>
       <x:c r="H23" s="22" t="str">
-        <x:v>Literal start address</x:v>
+        <x:v>Device Index</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -1522,23 +1522,23 @@
         <x:v>M485E::ManualWrite</x:v>
       </x:c>
       <x:c r="B24" s="22" t="str">
-        <x:v>Quantity</x:v>
+        <x:v>StartAddress</x:v>
       </x:c>
       <x:c r="C24" s="22" t="str">
-        <x:v>M485E::ManualWrite::Quantity</x:v>
+        <x:v>M485E::ManualWrite::StartAddress</x:v>
       </x:c>
       <x:c r="D24" s="22" t="str">
         <x:v>int32</x:v>
       </x:c>
       <x:c r="E24" s="22" t="str"/>
       <x:c r="F24" s="22" t="str">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G24" s="22" t="str">
         <x:v>Numeric input</x:v>
       </x:c>
       <x:c r="H24" s="22" t="str">
-        <x:v>Register count from 1 to 122</x:v>
+        <x:v>Literal start address</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
@@ -1546,25 +1546,23 @@
         <x:v>M485E::ManualWrite</x:v>
       </x:c>
       <x:c r="B25" s="22" t="str">
-        <x:v>Data</x:v>
+        <x:v>Quantity</x:v>
       </x:c>
       <x:c r="C25" s="22" t="str">
-        <x:v>M485E::ManualWrite::Data</x:v>
+        <x:v>M485E::ManualWrite::Quantity</x:v>
       </x:c>
       <x:c r="D25" s="22" t="str">
-        <x:v>int32[]</x:v>
-      </x:c>
-      <x:c r="E25" s="22" t="str">
-        <x:v>122</x:v>
-      </x:c>
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E25" s="22" t="str"/>
       <x:c r="F25" s="22" t="str">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G25" s="22" t="str">
-        <x:v>Array input</x:v>
+        <x:v>Numeric input</x:v>
       </x:c>
       <x:c r="H25" s="22" t="str">
-        <x:v>Register values stored in 32-bit elements</x:v>
+        <x:v>Register count from 1 to 122</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
@@ -1572,23 +1570,25 @@
         <x:v>M485E::ManualWrite</x:v>
       </x:c>
       <x:c r="B26" s="22" t="str">
-        <x:v>Send</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="C26" s="22" t="str">
-        <x:v>M485E::ManualWrite::Send</x:v>
+        <x:v>M485E::ManualWrite::Data</x:v>
       </x:c>
       <x:c r="D26" s="22" t="str">
-        <x:v>int32</x:v>
-      </x:c>
-      <x:c r="E26" s="22" t="str"/>
+        <x:v>int32[]</x:v>
+      </x:c>
+      <x:c r="E26" s="22" t="str">
+        <x:v>122</x:v>
+      </x:c>
       <x:c r="F26" s="22" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G26" s="22" t="str">
-        <x:v>Momentary button</x:v>
+        <x:v>Array input</x:v>
       </x:c>
       <x:c r="H26" s="22" t="str">
-        <x:v>Manual Register Write command</x:v>
+        <x:v>Register values stored in 32-bit elements</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -1596,10 +1596,10 @@
         <x:v>M485E::ManualWrite</x:v>
       </x:c>
       <x:c r="B27" s="23" t="str">
-        <x:v>ResultCode</x:v>
+        <x:v>Send</x:v>
       </x:c>
       <x:c r="C27" s="23" t="str">
-        <x:v>M485E::ManualWrite::ResultCode</x:v>
+        <x:v>M485E::ManualWrite::Send</x:v>
       </x:c>
       <x:c r="D27" s="23" t="str">
         <x:v>int32</x:v>
@@ -1609,21 +1609,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G27" s="23" t="str">
-        <x:v>Numeric display</x:v>
+        <x:v>Momentary button</x:v>
       </x:c>
       <x:c r="H27" s="23" t="str">
-        <x:v>Manual Write result</x:v>
+        <x:v>Manual Register Write command</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
       <x:c r="A28" s="23" t="str">
-        <x:v>M485E::SignalControl</x:v>
+        <x:v>M485E::ManualWrite</x:v>
       </x:c>
       <x:c r="B28" s="23" t="str">
-        <x:v>Index</x:v>
+        <x:v>ResultCode</x:v>
       </x:c>
       <x:c r="C28" s="23" t="str">
-        <x:v>M485E::SignalControl::Index</x:v>
+        <x:v>M485E::ManualWrite::ResultCode</x:v>
       </x:c>
       <x:c r="D28" s="23" t="str">
         <x:v>int32</x:v>
@@ -1633,10 +1633,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G28" s="23" t="str">
-        <x:v>Numeric input</x:v>
+        <x:v>Numeric display</x:v>
       </x:c>
       <x:c r="H28" s="23" t="str">
-        <x:v>Device Index</x:v>
+        <x:v>Manual Write result</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
@@ -1644,21 +1644,23 @@
         <x:v>M485E::SignalControl</x:v>
       </x:c>
       <x:c r="B29" s="23" t="str">
-        <x:v>SignalName</x:v>
+        <x:v>Index</x:v>
       </x:c>
       <x:c r="C29" s="23" t="str">
-        <x:v>M485E::SignalControl::SignalName</x:v>
+        <x:v>M485E::SignalControl::Index</x:v>
       </x:c>
       <x:c r="D29" s="23" t="str">
-        <x:v>string</x:v>
+        <x:v>int32</x:v>
       </x:c>
       <x:c r="E29" s="23" t="str"/>
-      <x:c r="F29" s="23" t="str"/>
+      <x:c r="F29" s="23" t="str">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="G29" s="23" t="str">
-        <x:v>Text input</x:v>
+        <x:v>Numeric input</x:v>
       </x:c>
       <x:c r="H29" s="23" t="str">
-        <x:v>Case-sensitive SignalName</x:v>
+        <x:v>Device Index</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -1666,23 +1668,21 @@
         <x:v>M485E::SignalControl</x:v>
       </x:c>
       <x:c r="B30" s="23" t="str">
-        <x:v>PhysicalValue</x:v>
+        <x:v>SignalName</x:v>
       </x:c>
       <x:c r="C30" s="23" t="str">
-        <x:v>M485E::SignalControl::PhysicalValue</x:v>
+        <x:v>M485E::SignalControl::SignalName</x:v>
       </x:c>
       <x:c r="D30" s="23" t="str">
-        <x:v>float64</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="E30" s="23" t="str"/>
-      <x:c r="F30" s="23" t="str">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="F30" s="23" t="str"/>
       <x:c r="G30" s="23" t="str">
-        <x:v>Numeric input/display</x:v>
+        <x:v>Text input</x:v>
       </x:c>
       <x:c r="H30" s="23" t="str">
-        <x:v>Signal physical value</x:v>
+        <x:v>Case-sensitive SignalName</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -1690,23 +1690,23 @@
         <x:v>M485E::SignalControl</x:v>
       </x:c>
       <x:c r="B31" s="23" t="str">
-        <x:v>Read</x:v>
+        <x:v>PhysicalValue</x:v>
       </x:c>
       <x:c r="C31" s="23" t="str">
-        <x:v>M485E::SignalControl::Read</x:v>
+        <x:v>M485E::SignalControl::PhysicalValue</x:v>
       </x:c>
       <x:c r="D31" s="23" t="str">
-        <x:v>int32</x:v>
+        <x:v>float64</x:v>
       </x:c>
       <x:c r="E31" s="23" t="str"/>
       <x:c r="F31" s="23" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G31" s="23" t="str">
-        <x:v>Momentary button</x:v>
+        <x:v>Numeric input/display</x:v>
       </x:c>
       <x:c r="H31" s="23" t="str">
-        <x:v>Signal Read command</x:v>
+        <x:v>Signal physical value</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -1714,10 +1714,10 @@
         <x:v>M485E::SignalControl</x:v>
       </x:c>
       <x:c r="B32" s="23" t="str">
-        <x:v>Write</x:v>
+        <x:v>Read</x:v>
       </x:c>
       <x:c r="C32" s="23" t="str">
-        <x:v>M485E::SignalControl::Write</x:v>
+        <x:v>M485E::SignalControl::Read</x:v>
       </x:c>
       <x:c r="D32" s="23" t="str">
         <x:v>int32</x:v>
@@ -1730,7 +1730,7 @@
         <x:v>Momentary button</x:v>
       </x:c>
       <x:c r="H32" s="23" t="str">
-        <x:v>Signal Write command</x:v>
+        <x:v>Signal Read command</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
@@ -1738,10 +1738,10 @@
         <x:v>M485E::SignalControl</x:v>
       </x:c>
       <x:c r="B33" s="23" t="str">
-        <x:v>ResultCode</x:v>
+        <x:v>Write</x:v>
       </x:c>
       <x:c r="C33" s="23" t="str">
-        <x:v>M485E::SignalControl::ResultCode</x:v>
+        <x:v>M485E::SignalControl::Write</x:v>
       </x:c>
       <x:c r="D33" s="23" t="str">
         <x:v>int32</x:v>
@@ -1751,16 +1751,40 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G33" s="23" t="str">
+        <x:v>Momentary button</x:v>
+      </x:c>
+      <x:c r="H33" s="23" t="str">
+        <x:v>Signal Write command</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>M485E::SignalControl</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>ResultCode</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>M485E::SignalControl::ResultCode</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>int32</x:v>
+      </x:c>
+      <x:c r="E34" t="str"/>
+      <x:c r="F34" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
         <x:v>Numeric display</x:v>
       </x:c>
-      <x:c r="H33" s="23" t="str">
+      <x:c r="H34" t="str">
         <x:v>Signal operation result</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c3d6ad5cd264dc2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6716360045a641d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>